--- a/backend/reportes/Reporte_CAD.xlsx
+++ b/backend/reportes/Reporte_CAD.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C3IN-ACO1-001-SS</t>
+          <t>B-CAD-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>773</v>
+        <v>177</v>
       </c>
       <c r="D2" t="n">
-        <v>101.6</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>76.2</v>
+        <v>4.76</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -508,14 +508,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO1-001-SS.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\B-CAD-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C3IN-ACO1-002-P</t>
+          <t>B-CAD-004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>773</v>
+        <v>300.54</v>
       </c>
       <c r="D3" t="n">
-        <v>251.91</v>
+        <v>157.11</v>
       </c>
       <c r="E3" t="n">
-        <v>6.35</v>
+        <v>4.76</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -540,25 +540,21 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>773</v>
-      </c>
-      <c r="J3" t="n">
-        <v>251.91</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO1-002-P.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\B-CAD-004.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C3IN-ACO1-003-SS</t>
+          <t>C3-ACF-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -567,13 +563,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2438.4</v>
+        <v>815</v>
       </c>
       <c r="D4" t="n">
-        <v>101.6</v>
+        <v>76.2</v>
       </c>
       <c r="E4" t="n">
-        <v>101.6</v>
+        <v>50.8</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -590,14 +586,14 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO1-003-SS.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-ACF-05.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C3IN-ACO2-001-SS</t>
+          <t>C3-BQ-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -606,13 +602,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>849</v>
+        <v>2493.08</v>
       </c>
       <c r="D5" t="n">
-        <v>76.2</v>
+        <v>576.89</v>
       </c>
       <c r="E5" t="n">
-        <v>76.2</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -622,21 +618,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2414.25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>779.63</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO2-001-SS.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-BQ-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C3IN-ACO2-002-TL</t>
+          <t>C3-BQ-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>863.09</v>
+        <v>515.7</v>
       </c>
       <c r="D6" t="n">
-        <v>101.6</v>
+        <v>114</v>
       </c>
       <c r="E6" t="n">
-        <v>76.2</v>
+        <v>9.52</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -661,21 +661,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>515.66</v>
+      </c>
+      <c r="J6" t="n">
+        <v>114</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO2-002-TL.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-BQ-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C3IN-ACO2-003-P</t>
+          <t>C3-BQ-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -684,13 +688,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>849</v>
+        <v>258.01</v>
       </c>
       <c r="D7" t="n">
-        <v>284.32</v>
+        <v>76.2</v>
       </c>
       <c r="E7" t="n">
-        <v>6.35</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -700,25 +704,21 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>849</v>
-      </c>
-      <c r="J7" t="n">
-        <v>284.32</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO2-003-P.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-BQ-11.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C3IN-ACO3-001-SS</t>
+          <t>C3-BQ-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>849</v>
+        <v>395.91</v>
       </c>
       <c r="D8" t="n">
         <v>76.2</v>
       </c>
       <c r="E8" t="n">
-        <v>76.2</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -743,21 +743,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>395.91</v>
+      </c>
+      <c r="J8" t="n">
+        <v>76.20999999999999</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO3-001-SS.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-BQ-13.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C3IN-ACO3-002-P</t>
+          <t>C3-BR1-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -766,13 +770,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>849</v>
+        <v>63.5</v>
       </c>
       <c r="D9" t="n">
-        <v>203.31</v>
+        <v>63.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6.35</v>
+        <v>51</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -782,25 +786,21 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>849</v>
-      </c>
-      <c r="J9" t="n">
-        <v>203.31</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACO3-002-P.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-BR1-05.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C3IN-ACRZ-01-A</t>
+          <t>C3-ESC-01-NV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2780</v>
+        <v>367</v>
       </c>
       <c r="D10" t="n">
-        <v>380.46</v>
+        <v>50.8</v>
       </c>
       <c r="E10" t="n">
-        <v>9.52</v>
+        <v>38.74</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -825,25 +825,21 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J10" t="n">
-        <v>380.46</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACRZ-01-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-ESC-01-NV.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C3IN-ACRZ-01</t>
+          <t>C3-ESC-06-NV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -852,13 +848,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2780</v>
+        <v>2606</v>
       </c>
       <c r="D11" t="n">
-        <v>380.46</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>9.52</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -868,25 +864,21 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J11" t="n">
-        <v>380.46</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACRZ-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-ESC-06-NV.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C3IN-ACRZ-02</t>
+          <t>C3-NBDX-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -895,13 +887,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1130</v>
+        <v>827</v>
       </c>
       <c r="D12" t="n">
-        <v>386.39</v>
+        <v>50.8</v>
       </c>
       <c r="E12" t="n">
-        <v>9.52</v>
+        <v>50.8</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -911,25 +903,21 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1130</v>
-      </c>
-      <c r="J12" t="n">
-        <v>386.39</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACRZ-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-NBDX-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C3IN-ACRZ-03</t>
+          <t>C3-NBDX-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -938,13 +926,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>500</v>
+        <v>350.93</v>
       </c>
       <c r="D13" t="n">
-        <v>367.39</v>
+        <v>141.92</v>
       </c>
       <c r="E13" t="n">
-        <v>9.52</v>
+        <v>19.05</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -958,21 +946,21 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>500</v>
+        <v>296.54</v>
       </c>
       <c r="J13" t="n">
-        <v>367.39</v>
+        <v>225.98</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Acorazado\C3IN-ACRZ-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-NBDX-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C3IN-ALMUR-01-A</t>
+          <t>C3-NBDX-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,13 +969,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1834.43</v>
+        <v>176.7</v>
       </c>
       <c r="D14" t="n">
-        <v>550.97</v>
+        <v>117.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4</v>
+        <v>19.05</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -997,25 +985,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1834.43</v>
-      </c>
-      <c r="J14" t="n">
-        <v>550.97</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-ALMUR-01-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-NBDX-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C3IN-ALMUR-01</t>
+          <t>C3-NBDX-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1024,13 +1008,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1834.43</v>
+        <v>755</v>
       </c>
       <c r="D15" t="n">
-        <v>550.97</v>
+        <v>63.5</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4</v>
+        <v>63.5</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -1040,25 +1024,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1834.43</v>
-      </c>
-      <c r="J15" t="n">
-        <v>550.97</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-ALMUR-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-NBDX-04.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C3IN-CFJAL-01</t>
+          <t>C3-NPS-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1067,13 +1047,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1320</v>
+        <v>355.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1089.77</v>
+        <v>114.3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.35</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -1083,25 +1063,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1089.77</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-CFJAL-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\C3-NPS-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C3IN-PBC-01</t>
+          <t>CAS-ALMU-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1110,10 +1086,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1000</v>
+        <v>168.15</v>
       </c>
       <c r="D17" t="n">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
         <v>6.35</v>
@@ -1130,21 +1106,21 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>168.15</v>
       </c>
       <c r="J17" t="n">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-PBC-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CAS-ALMU-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C3IN-RCA-01</t>
+          <t>CAS-ALMU-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1153,13 +1129,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2109</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>868.2</v>
+        <v>31.75</v>
       </c>
       <c r="E18" t="n">
-        <v>6.35</v>
+        <v>31.75</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -1169,25 +1145,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2109</v>
-      </c>
-      <c r="J18" t="n">
-        <v>868.2</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-RCA-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CAS-ALMU-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C3IN-RCA-02</t>
+          <t>CAS-RRAR-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,13 +1168,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>250</v>
+        <v>1872.85</v>
       </c>
       <c r="D19" t="n">
-        <v>22.22</v>
+        <v>590.0700000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>22.22</v>
+        <v>6.35</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -1212,21 +1184,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1872.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>590.0700000000001</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-RCA-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CAS-RRAR-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C3IN-RCA-03</t>
+          <t>CSC-BAS-001-L-D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1235,10 +1211,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2109</v>
+        <v>3000</v>
       </c>
       <c r="D20" t="n">
-        <v>868.2</v>
+        <v>269.15</v>
       </c>
       <c r="E20" t="n">
         <v>6.35</v>
@@ -1255,21 +1231,21 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2109</v>
+        <v>3000</v>
       </c>
       <c r="J20" t="n">
-        <v>868.2</v>
+        <v>269.15</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-RCA-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BAS-001-L-D.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C3IN-SOBD-01</t>
+          <t>CSC-BAS-002-L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1278,13 +1254,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1652</v>
+        <v>101.6</v>
       </c>
       <c r="D21" t="n">
-        <v>725.3200000000001</v>
+        <v>101.6</v>
       </c>
       <c r="E21" t="n">
-        <v>6.35</v>
+        <v>3.18</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1298,21 +1274,21 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1652</v>
+        <v>101.6</v>
       </c>
       <c r="J21" t="n">
-        <v>725.3200000000001</v>
+        <v>101.6</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Aluminio\C3IN-SOBD-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BAS-002-L.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C3-IN-BAQ-01</t>
+          <t>CSC-BAS-003-P-D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1321,13 +1297,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>872</v>
+        <v>316.18</v>
       </c>
       <c r="D22" t="n">
-        <v>214.02</v>
+        <v>101.6</v>
       </c>
       <c r="E22" t="n">
-        <v>6.35</v>
+        <v>9.52</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -1337,21 +1313,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="J22" t="n">
+        <v>101.6</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Base de quinta\C3-IN-BAQ-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BAS-003-P-D.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C3-IN-BAQ-02</t>
+          <t>CSC-BQ-04-L</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,13 +1340,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>872</v>
+        <v>897</v>
       </c>
       <c r="D23" t="n">
-        <v>101.6</v>
+        <v>76.2</v>
       </c>
       <c r="E23" t="n">
-        <v>76.2</v>
+        <v>9.52</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -1376,21 +1356,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>897</v>
+      </c>
+      <c r="J23" t="n">
+        <v>76.2</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Base de quinta\C3-IN-BAQ-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BQ-04-L.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C3IN-CAM-01</t>
+          <t>CSC-BQ-07-SG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1399,13 +1383,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2230</v>
+        <v>1338.6</v>
       </c>
       <c r="D24" t="n">
-        <v>50.8</v>
+        <v>152.4</v>
       </c>
       <c r="E24" t="n">
-        <v>50.8</v>
+        <v>76.2</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -1422,14 +1406,14 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BQ-07-SG.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C3IN-CAM-02</t>
+          <t>CSC-BQ-08-SG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1438,13 +1422,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>744</v>
+        <v>1552.35</v>
       </c>
       <c r="D25" t="n">
-        <v>50.8</v>
+        <v>101.6</v>
       </c>
       <c r="E25" t="n">
-        <v>50.8</v>
+        <v>76.2</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -1461,14 +1445,14 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BQ-08-SG.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C3IN-CAM-03</t>
+          <t>CSC-BQ-09-P</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1477,10 +1461,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>150</v>
+        <v>1552.35</v>
       </c>
       <c r="D26" t="n">
-        <v>130</v>
+        <v>101.6</v>
       </c>
       <c r="E26" t="n">
         <v>9.52</v>
@@ -1497,21 +1481,21 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>150</v>
+        <v>1552.35</v>
       </c>
       <c r="J26" t="n">
-        <v>130</v>
+        <v>101.6</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BQ-09-P.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C3IN-CAM-04-A</t>
+          <t>CSC-BR3-001-SS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1520,13 +1504,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1366.01</v>
+        <v>1356</v>
       </c>
       <c r="D27" t="n">
-        <v>880.6900000000001</v>
+        <v>76.2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.18</v>
+        <v>76.2</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -1536,25 +1520,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1366.01</v>
-      </c>
-      <c r="J27" t="n">
-        <v>880.6900000000001</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-04-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BR3-001-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C3IN-CAM-04</t>
+          <t>CSC-BR3-003-SS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1563,13 +1543,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1366.01</v>
+        <v>1520</v>
       </c>
       <c r="D28" t="n">
-        <v>880.6900000000001</v>
+        <v>63.5</v>
       </c>
       <c r="E28" t="n">
-        <v>3.18</v>
+        <v>63.5</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -1579,25 +1559,21 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1366.01</v>
-      </c>
-      <c r="J28" t="n">
-        <v>880.6900000000001</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-04.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BR3-003-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C3IN-CAM-05-A</t>
+          <t>CSC-BR4-00-P</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,13 +1582,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>992.36</v>
+        <v>74.2</v>
       </c>
       <c r="D29" t="n">
-        <v>849</v>
+        <v>74.2</v>
       </c>
       <c r="E29" t="n">
-        <v>3.18</v>
+        <v>9.52</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -1622,25 +1598,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>992.36</v>
-      </c>
-      <c r="J29" t="n">
-        <v>849</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-05-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BR4-00-P.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C3IN-CAM-05</t>
+          <t>CSC-BR4-001-SS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1649,13 +1621,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>992.36</v>
+        <v>735.2</v>
       </c>
       <c r="D30" t="n">
-        <v>849</v>
+        <v>76.2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.18</v>
+        <v>76.2</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -1665,25 +1637,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>992.36</v>
-      </c>
-      <c r="J30" t="n">
-        <v>849</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-05.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BR4-001-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C3IN-CAM-06-A</t>
+          <t>CSC-BR4-002-TL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1692,13 +1660,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1000.74</v>
+        <v>857</v>
       </c>
       <c r="D31" t="n">
-        <v>881.71</v>
+        <v>63.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3.18</v>
+        <v>63.5</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -1708,25 +1676,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1000.74</v>
-      </c>
-      <c r="J31" t="n">
-        <v>881.71</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-06-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-BR4-002-TL.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C3IN-CAM-06</t>
+          <t>CSC-CH2-001-TL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1735,13 +1699,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1000.74</v>
+        <v>982</v>
       </c>
       <c r="D32" t="n">
-        <v>881.71</v>
+        <v>114.3</v>
       </c>
       <c r="E32" t="n">
-        <v>3.18</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -1751,25 +1715,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1000.74</v>
-      </c>
-      <c r="J32" t="n">
-        <v>881.71</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-06.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-CH2-001-TL.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C3IN-CAM-07</t>
+          <t>CSC-CH2-002-SS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1778,13 +1738,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>839</v>
+        <v>982</v>
       </c>
       <c r="D33" t="n">
-        <v>225</v>
+        <v>76.2</v>
       </c>
       <c r="E33" t="n">
-        <v>7.94</v>
+        <v>50.8</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -1794,25 +1754,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>839</v>
-      </c>
-      <c r="J33" t="n">
-        <v>225</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-07.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-CH2-002-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C3IN-CAM-08</t>
+          <t>CSC-COS-004-SS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1821,13 +1777,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>850</v>
+        <v>376.6</v>
       </c>
       <c r="D34" t="n">
-        <v>210.23</v>
+        <v>101.6</v>
       </c>
       <c r="E34" t="n">
-        <v>3.18</v>
+        <v>76.2</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -1837,25 +1793,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>850</v>
-      </c>
-      <c r="J34" t="n">
-        <v>210.23</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-08.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-COS-004-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C3IN-CAM-09</t>
+          <t>CSC-COS-007-SS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1864,13 +1816,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1190</v>
+        <v>1271</v>
       </c>
       <c r="D35" t="n">
-        <v>820</v>
+        <v>76.2</v>
       </c>
       <c r="E35" t="n">
-        <v>1.9</v>
+        <v>76.2</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -1880,25 +1832,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J35" t="n">
-        <v>820</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-09.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-COS-007-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C3IN-CAM-10</t>
+          <t>CSC-COS-008-TL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1907,13 +1855,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>908.49</v>
+        <v>1231</v>
       </c>
       <c r="D36" t="n">
-        <v>820</v>
+        <v>101.6</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9</v>
+        <v>76.2</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -1923,25 +1871,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>908.49</v>
-      </c>
-      <c r="J36" t="n">
-        <v>820</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-10.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-COS-008-TL.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C3IN-CAM-11</t>
+          <t>CSC-CU-002-W-D</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1950,13 +1894,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>628</v>
+        <v>303.1</v>
       </c>
       <c r="D37" t="n">
-        <v>300</v>
+        <v>25.4</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9</v>
+        <v>6.35</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -1966,25 +1910,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>628</v>
-      </c>
-      <c r="J37" t="n">
-        <v>300</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-11.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-CU-002-W-D.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C3IN-CAM-12</t>
+          <t>CSC-CU-005-SS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1993,13 +1933,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>734.26</v>
+        <v>645</v>
       </c>
       <c r="D38" t="n">
-        <v>400</v>
+        <v>25.4</v>
       </c>
       <c r="E38" t="n">
-        <v>3.18</v>
+        <v>25.4</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -2009,25 +1949,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>734.26</v>
-      </c>
-      <c r="J38" t="n">
-        <v>400</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-12.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-CU-005-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C3IN-CAM-13</t>
+          <t>CSC-PTX-001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2036,13 +1972,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>670</v>
+        <v>460</v>
       </c>
       <c r="D39" t="n">
-        <v>25.4</v>
+        <v>63.5</v>
       </c>
       <c r="E39" t="n">
-        <v>25.4</v>
+        <v>63.5</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -2059,14 +1995,14 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-13.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-PTX-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C3IN-CAM-14</t>
+          <t>CSC-PTX-002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2075,13 +2011,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>610</v>
+        <v>552.42</v>
       </c>
       <c r="D40" t="n">
-        <v>73.58</v>
+        <v>219.21</v>
       </c>
       <c r="E40" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -2095,21 +2031,21 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>610</v>
+        <v>552.42</v>
       </c>
       <c r="J40" t="n">
-        <v>73.58</v>
+        <v>219.21</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-14.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-PTX-002.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C3IN-CAM-15</t>
+          <t>CSC-RAR1-001-M</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2118,13 +2054,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>605</v>
+        <v>1879</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>101.6</v>
       </c>
       <c r="E41" t="n">
-        <v>7.94</v>
+        <v>40.2</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -2134,25 +2070,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>605</v>
-      </c>
-      <c r="J41" t="n">
-        <v>44</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-15.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-001-M.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C3IN-CAM-16</t>
+          <t>CSC-RAR1-002-SS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2161,13 +2093,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>850</v>
+        <v>1879</v>
       </c>
       <c r="D42" t="n">
-        <v>45</v>
+        <v>101.6</v>
       </c>
       <c r="E42" t="n">
-        <v>4.76</v>
+        <v>40.2</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -2177,25 +2109,21 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>850</v>
-      </c>
-      <c r="J42" t="n">
-        <v>45</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-16.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-002-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C3IN-CAM-17-A</t>
+          <t>CSC-RAR1-003-SS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2204,13 +2132,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>814.15</v>
+        <v>1879</v>
       </c>
       <c r="D43" t="n">
-        <v>703.28</v>
+        <v>101.6</v>
       </c>
       <c r="E43" t="n">
-        <v>1.9</v>
+        <v>40.2</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -2220,25 +2148,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>814.15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>703.28</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-17-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-003-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C3IN-CAM-17</t>
+          <t>CSC-RAR1-004-M</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2247,13 +2171,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>814.15</v>
+        <v>1879</v>
       </c>
       <c r="D44" t="n">
-        <v>703.28</v>
+        <v>101.6</v>
       </c>
       <c r="E44" t="n">
-        <v>1.9</v>
+        <v>40.2</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -2263,25 +2187,21 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>814.15</v>
-      </c>
-      <c r="J44" t="n">
-        <v>703.28</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-17.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-004-M.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C3IN-CAM-18-A</t>
+          <t>CSC-RAR1-005-SS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2290,13 +2210,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>704.95</v>
+        <v>2257</v>
       </c>
       <c r="D45" t="n">
-        <v>508</v>
+        <v>101.6</v>
       </c>
       <c r="E45" t="n">
-        <v>1.9</v>
+        <v>50.8</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -2306,25 +2226,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>704.95</v>
-      </c>
-      <c r="J45" t="n">
-        <v>508</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-18-A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-005-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C3IN-CAM-18</t>
+          <t>CSC-RAR1-006-P</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2333,13 +2249,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>704.95</v>
+        <v>620.71</v>
       </c>
       <c r="D46" t="n">
-        <v>508</v>
+        <v>125</v>
       </c>
       <c r="E46" t="n">
-        <v>1.9</v>
+        <v>6.35</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -2349,25 +2265,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>704.95</v>
-      </c>
-      <c r="J46" t="n">
-        <v>508</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-18.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-006-P.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C3IN-CAM-19</t>
+          <t>CSC-RAR1-007-P-Z</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2376,13 +2288,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2438.4</v>
+        <v>1879</v>
       </c>
       <c r="D47" t="n">
-        <v>76.2</v>
+        <v>620.53</v>
       </c>
       <c r="E47" t="n">
-        <v>76.2</v>
+        <v>6.35</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -2399,14 +2311,14 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-19.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-007-P-Z.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C3IN-CAM-20</t>
+          <t>CSC-RAR1-008-P</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2415,13 +2327,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>780</v>
+        <v>620.5</v>
       </c>
       <c r="D48" t="n">
-        <v>25.4</v>
+        <v>101.6</v>
       </c>
       <c r="E48" t="n">
-        <v>25.4</v>
+        <v>6.35</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -2438,14 +2350,14 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-20.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-008-P.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C3IN-CAM-21</t>
+          <t>CSC-RAR1-009-SS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2454,13 +2366,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>177.8</v>
+        <v>621</v>
       </c>
       <c r="D49" t="n">
-        <v>25.4</v>
+        <v>76.2</v>
       </c>
       <c r="E49" t="n">
-        <v>25.4</v>
+        <v>50.8</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -2477,14 +2389,14 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-21.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-009-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C3IN-CAM-22</t>
+          <t>CSC-RAR1-010-L</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2493,13 +2405,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3028</v>
+        <v>230.96</v>
       </c>
       <c r="D50" t="n">
-        <v>247.75</v>
+        <v>101.6</v>
       </c>
       <c r="E50" t="n">
-        <v>1.9</v>
+        <v>4.76</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -2509,25 +2421,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>3028</v>
-      </c>
-      <c r="J50" t="n">
-        <v>247.75</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-22.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-010-L.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C3IN-CAM-23</t>
+          <t>CSC-RAR1-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2536,13 +2444,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>550</v>
+        <v>458</v>
       </c>
       <c r="D51" t="n">
-        <v>290.54</v>
+        <v>99.5</v>
       </c>
       <c r="E51" t="n">
-        <v>4.76</v>
+        <v>3.18</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -2556,21 +2464,21 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>550</v>
+        <v>458</v>
       </c>
       <c r="J51" t="n">
-        <v>290.54</v>
+        <v>99.53</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-23.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR1-11.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C3IN-CAM-24</t>
+          <t>CSC-RAR2-001-TL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2579,13 +2487,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>786.6900000000001</v>
+        <v>1955</v>
       </c>
       <c r="D52" t="n">
-        <v>156.55</v>
+        <v>76.2</v>
       </c>
       <c r="E52" t="n">
-        <v>3.18</v>
+        <v>50.8</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -2595,25 +2503,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>786.6900000000001</v>
-      </c>
-      <c r="J52" t="n">
-        <v>156.55</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-24.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-001-TL.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C3IN-CAM-25</t>
+          <t>CSC-RAR2-002-SS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2622,13 +2526,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>240.06</v>
+        <v>1955</v>
       </c>
       <c r="D53" t="n">
-        <v>79.95999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="E53" t="n">
-        <v>4.76</v>
+        <v>50.8</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -2638,25 +2542,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>240.06</v>
-      </c>
-      <c r="J53" t="n">
-        <v>79.95999999999999</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\C3IN-CAM-25.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-002-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C3IN-CUEN-001</t>
+          <t>CSC-RAR2-003-L</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2665,10 +2565,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1160</v>
+        <v>596.9</v>
       </c>
       <c r="D54" t="n">
-        <v>686.3</v>
+        <v>76.2</v>
       </c>
       <c r="E54" t="n">
         <v>6.35</v>
@@ -2685,21 +2585,21 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1160</v>
+        <v>596.9</v>
       </c>
       <c r="J54" t="n">
-        <v>686.3</v>
+        <v>76.2</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\CUENCA ENSAMBLE\C3IN-CUEN-001.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-003-L.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C3IN-CUEN-002</t>
+          <t>CSC-RAR2-004-TL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2708,13 +2608,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>905</v>
+        <v>495.3</v>
       </c>
       <c r="D55" t="n">
-        <v>111.4</v>
+        <v>76.2</v>
       </c>
       <c r="E55" t="n">
-        <v>6.35</v>
+        <v>50.8</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -2724,25 +2624,21 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>905</v>
-      </c>
-      <c r="J55" t="n">
-        <v>111.4</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\CUENCA ENSAMBLE\C3IN-CUEN-002.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-004-TL.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C3IN-CUEN-003</t>
+          <t>CSC-RAR2-005-L-D</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2751,10 +2647,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="D56" t="n">
-        <v>169.05</v>
+        <v>131.87</v>
       </c>
       <c r="E56" t="n">
         <v>4.76</v>
@@ -2771,21 +2667,21 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="J56" t="n">
-        <v>169.05</v>
+        <v>131.87</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Cama\CUENCA ENSAMBLE\C3IN-CUEN-003.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-005-L-D.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-01</t>
+          <t>CSC-RAR2-006-SS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2794,13 +2690,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2489.2</v>
+        <v>1041.4</v>
       </c>
       <c r="D57" t="n">
-        <v>63.5</v>
+        <v>152.4</v>
       </c>
       <c r="E57" t="n">
-        <v>63.5</v>
+        <v>76.2</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -2817,14 +2713,14 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\CSC-RAR2-006-SS.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-02</t>
+          <t>EXTATR-002</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2833,13 +2729,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>910</v>
+        <v>894.41</v>
       </c>
       <c r="D58" t="n">
-        <v>131.87</v>
+        <v>684.41</v>
       </c>
       <c r="E58" t="n">
-        <v>4.76</v>
+        <v>3.4</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -2849,25 +2745,21 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>910</v>
-      </c>
-      <c r="J58" t="n">
-        <v>131.87</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\EXTATR-002.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-03</t>
+          <t>EXTATR-003</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2876,13 +2768,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2600.33</v>
+        <v>526.61</v>
       </c>
       <c r="D59" t="n">
-        <v>228.6</v>
+        <v>448.72</v>
       </c>
       <c r="E59" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -2892,25 +2784,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>2600.32</v>
-      </c>
-      <c r="J59" t="n">
-        <v>228.6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\EXTATR-003.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-04</t>
+          <t>F1-CHAR-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2919,13 +2807,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>330.2</v>
+        <v>2422.53</v>
       </c>
       <c r="D60" t="n">
-        <v>88.89</v>
+        <v>648.29</v>
       </c>
       <c r="E60" t="n">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -2935,25 +2823,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>330.2</v>
-      </c>
-      <c r="J60" t="n">
-        <v>88.90000000000001</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-04.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\F1-CHAR-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-05</t>
+          <t>HO2-COS-V01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2962,13 +2846,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>330.2</v>
+        <v>4236.44</v>
       </c>
       <c r="D61" t="n">
-        <v>88.89</v>
+        <v>400.49</v>
       </c>
       <c r="E61" t="n">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -2982,21 +2866,21 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>330.2</v>
+        <v>4241.2</v>
       </c>
       <c r="J61" t="n">
-        <v>88.90000000000001</v>
+        <v>400.49</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-05.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\HO2-COS-V01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-06</t>
+          <t>R1BEL-CO-037</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3005,13 +2889,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>50.8</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>50.8</v>
       </c>
       <c r="E62" t="n">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -3025,21 +2909,21 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>65</v>
+        <v>50.8</v>
       </c>
       <c r="J62" t="n">
-        <v>60</v>
+        <v>50.8</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-06.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CO-037.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-07 - copia</t>
+          <t>R1BEL-CO-055</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3048,13 +2932,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>928</v>
+        <v>2446.8</v>
       </c>
       <c r="D63" t="n">
-        <v>76.2</v>
+        <v>15.88</v>
       </c>
       <c r="E63" t="n">
-        <v>76.2</v>
+        <v>15.88</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -3071,14 +2955,14 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-07 - copia.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CO-055.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-07</t>
+          <t>R1BEL-CO-056</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3087,13 +2971,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>928</v>
+        <v>2783</v>
       </c>
       <c r="D64" t="n">
-        <v>76.2</v>
+        <v>15.88</v>
       </c>
       <c r="E64" t="n">
-        <v>76.2</v>
+        <v>15.88</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -3110,14 +2994,14 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-07.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CO-056.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-08 - copia</t>
+          <t>R1BEL-CO-057</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3126,13 +3010,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>928</v>
+        <v>2705</v>
       </c>
       <c r="D65" t="n">
-        <v>63.5</v>
+        <v>15.88</v>
       </c>
       <c r="E65" t="n">
-        <v>63.5</v>
+        <v>15.88</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
@@ -3149,14 +3033,14 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-08 - copia.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CO-057.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-08</t>
+          <t>R1BEL-CUEN-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3165,13 +3049,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>928</v>
+        <v>807.62</v>
       </c>
       <c r="D66" t="n">
-        <v>63.5</v>
+        <v>147.35</v>
       </c>
       <c r="E66" t="n">
-        <v>63.5</v>
+        <v>6.35</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
@@ -3188,14 +3072,14 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-08.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CUEN-05.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-09</t>
+          <t>R1BEL-CUEN-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3204,13 +3088,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2590.8</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
-        <v>50.8</v>
+        <v>38.1</v>
       </c>
       <c r="E67" t="n">
-        <v>50.8</v>
+        <v>38.1</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
@@ -3227,14 +3111,14 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-09.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CUEN-06.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-12</t>
+          <t>R1BEL-CUEN-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3243,13 +3127,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>924</v>
+        <v>38.1</v>
       </c>
       <c r="D68" t="n">
         <v>38.1</v>
       </c>
       <c r="E68" t="n">
-        <v>38.1</v>
+        <v>1.9</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
@@ -3266,14 +3150,14 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-12.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-CUEN-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-13</t>
+          <t>R1BEL-ESCO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3282,13 +3166,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>160</v>
+        <v>646</v>
       </c>
       <c r="D69" t="n">
-        <v>50.8</v>
+        <v>45.4</v>
       </c>
       <c r="E69" t="n">
-        <v>50.8</v>
+        <v>4.76</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
@@ -3305,14 +3189,14 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-13.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-ESCO.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-14</t>
+          <t>R1BEL-ESCO2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3321,13 +3205,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>990</v>
+        <v>646</v>
       </c>
       <c r="D70" t="n">
-        <v>50.8</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>50.8</v>
+        <v>3.18</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
@@ -3344,14 +3228,14 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-14.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-ESCO2.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-15</t>
+          <t>R1BEL-ST-NV-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3360,13 +3244,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1124</v>
+        <v>367</v>
       </c>
       <c r="D71" t="n">
         <v>50.8</v>
       </c>
       <c r="E71" t="n">
-        <v>50.8</v>
+        <v>38.74</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
@@ -3383,14 +3267,14 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-15.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-ST-NV-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-16</t>
+          <t>R1BEL-ST-NV-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3399,13 +3283,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2489.2</v>
+        <v>2795</v>
       </c>
       <c r="D72" t="n">
-        <v>63.5</v>
+        <v>50.8</v>
       </c>
       <c r="E72" t="n">
-        <v>63.5</v>
+        <v>2795</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
@@ -3422,14 +3306,14 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-16.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-ST-NV-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-17</t>
+          <t>R1BEL-ST-NV-02A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3438,13 +3322,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>191.63</v>
+        <v>2822</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8</v>
+        <v>50.8</v>
       </c>
       <c r="E73" t="n">
-        <v>3.18</v>
+        <v>2822</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
@@ -3454,25 +3338,21 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>191.63</v>
-      </c>
-      <c r="J73" t="n">
-        <v>177.8</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-17.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1BEL-ST-NV-02A.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C3IN-CFJ-18</t>
+          <t>R1MAR-B6-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3481,13 +3361,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>63.5</v>
+        <v>2438</v>
       </c>
       <c r="D74" t="n">
-        <v>50.8</v>
+        <v>101.6</v>
       </c>
       <c r="E74" t="n">
-        <v>12.7</v>
+        <v>2438</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
@@ -3504,14 +3384,14 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJ-18.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C3IN-CFJAL-02</t>
+          <t>R1MAR-B6-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3520,13 +3400,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>979.24</v>
+        <v>850.9</v>
       </c>
       <c r="D75" t="n">
-        <v>959.97</v>
+        <v>50.8</v>
       </c>
       <c r="E75" t="n">
-        <v>6.35</v>
+        <v>850.9</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
@@ -3536,25 +3416,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>979.24</v>
-      </c>
-      <c r="J75" t="n">
-        <v>959.97</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJAL-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C3IN-CFJAL-02A</t>
+          <t>R1MAR-B6-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3563,13 +3439,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>979.2</v>
+        <v>2285.6</v>
       </c>
       <c r="D76" t="n">
-        <v>960</v>
+        <v>50.8</v>
       </c>
       <c r="E76" t="n">
-        <v>6.35</v>
+        <v>2285.6</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
@@ -3579,25 +3455,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>979.24</v>
-      </c>
-      <c r="J76" t="n">
-        <v>959.97</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJAL-02A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C3IN-CFJAL-03</t>
+          <t>R1MAR-B6-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3606,13 +3478,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>878</v>
+        <v>578</v>
       </c>
       <c r="D77" t="n">
         <v>76.2</v>
       </c>
       <c r="E77" t="n">
-        <v>6.35</v>
+        <v>578</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
@@ -3622,25 +3494,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>878</v>
-      </c>
-      <c r="J77" t="n">
-        <v>76.2</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete fijo\C3IN-CFJAL-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-04.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C3IN-CMOV-01</t>
+          <t>R1MAR-B6-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3649,13 +3517,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>910</v>
+        <v>2108.2</v>
       </c>
       <c r="D78" t="n">
-        <v>63.5</v>
+        <v>76.2</v>
       </c>
       <c r="E78" t="n">
-        <v>63.5</v>
+        <v>2108.2</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -3672,14 +3540,14 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete móvil\C3IN-CMOV-01.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-05.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C3IN-CMOV-02</t>
+          <t>R1MAR-B6-06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3688,13 +3556,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2476.5</v>
+        <v>2058</v>
       </c>
       <c r="D79" t="n">
-        <v>63.5</v>
+        <v>253.29</v>
       </c>
       <c r="E79" t="n">
-        <v>63.5</v>
+        <v>6.35</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
@@ -3711,14 +3579,14 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete móvil\C3IN-CMOV-02.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-06.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C3IN-CMOV-03</t>
+          <t>R1MAR-B6-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3727,13 +3595,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>910</v>
+        <v>203</v>
       </c>
       <c r="D80" t="n">
-        <v>50.8</v>
+        <v>101.6</v>
       </c>
       <c r="E80" t="n">
-        <v>50.8</v>
+        <v>203</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
@@ -3750,14 +3618,14 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete móvil\C3IN-CMOV-03.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C3IN-CMOV-04</t>
+          <t>R1MAR-B6-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3766,10 +3634,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>729</v>
+        <v>254</v>
       </c>
       <c r="D81" t="n">
-        <v>50.8</v>
+        <v>101.6</v>
       </c>
       <c r="E81" t="n">
         <v>50.8</v>
@@ -3789,14 +3657,14 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete móvil\C3IN-CMOV-04.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-08.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C3IN-CMOV-05</t>
+          <t>R1MAR-B6-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3805,13 +3673,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>858.6</v>
+        <v>635.9</v>
       </c>
       <c r="D82" t="n">
-        <v>729</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>3.18</v>
+        <v>9.52</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
@@ -3821,25 +3689,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>858.6</v>
-      </c>
-      <c r="J82" t="n">
-        <v>729</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Copete móvil\C3IN-CMOV-05.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-09.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C3IN-SD-001</t>
+          <t>R1MAR-B6-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3848,13 +3712,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7408.1</v>
+        <v>232.4</v>
       </c>
       <c r="D83" t="n">
-        <v>152.4</v>
+        <v>101.6</v>
       </c>
       <c r="E83" t="n">
-        <v>76.2</v>
+        <v>9.52</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
@@ -3871,14 +3735,14 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-001.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-10.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C3IN-SD-002</t>
+          <t>R1MAR-B6-11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3887,13 +3751,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3730.6</v>
+        <v>297</v>
       </c>
       <c r="D84" t="n">
-        <v>983.5599999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>6.35</v>
+        <v>7.94</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
@@ -3907,21 +3771,21 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3730.6</v>
+        <v>297.04</v>
       </c>
       <c r="J84" t="n">
-        <v>983.5599999999999</v>
+        <v>73.05</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-002.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-B6-11.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C3IN-SD-003</t>
+          <t>R1MAR-CHAQ7-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3930,13 +3794,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3400</v>
+        <v>1075</v>
       </c>
       <c r="D85" t="n">
-        <v>152.4</v>
+        <v>76.2</v>
       </c>
       <c r="E85" t="n">
-        <v>50.8</v>
+        <v>1075</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
@@ -3953,14 +3817,14 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-003.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-CHAQ7-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C3IN-SD-003A</t>
+          <t>R1MAR-CHAQ7-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3969,13 +3833,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3400</v>
+        <v>950</v>
       </c>
       <c r="D86" t="n">
-        <v>152.4</v>
+        <v>114.3</v>
       </c>
       <c r="E86" t="n">
-        <v>50.8</v>
+        <v>950</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
@@ -3992,14 +3856,14 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-003A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-CHAQ7-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C3IN-SD-004</t>
+          <t>R1MAR-CTD-001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4008,13 +3872,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2759.79</v>
+        <v>127</v>
       </c>
       <c r="D87" t="n">
-        <v>1370.04</v>
+        <v>76.2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.76</v>
+        <v>50.8</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -4024,25 +3888,21 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>2759.79</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1370.04</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-004.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-CTD-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C3IN-SD-005</t>
+          <t>R1MAR-RAR2-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4051,13 +3911,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1555.24</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>435.3</v>
+        <v>31.1</v>
       </c>
       <c r="E88" t="n">
-        <v>6.35</v>
+        <v>9.52</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -4067,25 +3927,21 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>1383.24</v>
-      </c>
-      <c r="J88" t="n">
-        <v>435.3</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-005.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-RAR2-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C3IN-SD-006</t>
+          <t>R1MAR-RAR2-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4094,13 +3950,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2725</v>
+        <v>607</v>
       </c>
       <c r="D89" t="n">
-        <v>101.6</v>
+        <v>228.6</v>
       </c>
       <c r="E89" t="n">
-        <v>76.2</v>
+        <v>9.52</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
@@ -4117,14 +3973,14 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-006.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-RAR2-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C3IN-SD-007</t>
+          <t>R1MAR-RARC-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4133,13 +3989,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2725</v>
+        <v>948.8</v>
       </c>
       <c r="D90" t="n">
-        <v>101.6</v>
+        <v>76.2</v>
       </c>
       <c r="E90" t="n">
-        <v>76.2</v>
+        <v>948.8</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -4156,14 +4012,14 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-007.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-RARC-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C3IN-SD-008</t>
+          <t>R1MAR-TDM-001</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4172,13 +4028,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7580</v>
+        <v>165.6</v>
       </c>
       <c r="D91" t="n">
-        <v>101.6</v>
+        <v>162.6</v>
       </c>
       <c r="E91" t="n">
-        <v>50.8</v>
+        <v>9.52</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
@@ -4195,14 +4051,14 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-008.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R1MAR-TDM-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C3IN-SD-009</t>
+          <t>R25-AC-AL-02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4211,13 +4067,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>847.39</v>
+        <v>2334.4</v>
       </c>
       <c r="D92" t="n">
-        <v>435.3</v>
+        <v>868.3099999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>9.52</v>
+        <v>1.9</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
@@ -4231,21 +4087,21 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>809.29</v>
+        <v>2334.4</v>
       </c>
       <c r="J92" t="n">
-        <v>435.3</v>
+        <v>868.3099999999999</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-009.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-AC-AL-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C3IN-SD-010</t>
+          <t>R25-ARR1-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4254,13 +4110,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2725</v>
+        <v>2300</v>
       </c>
       <c r="D93" t="n">
         <v>101.6</v>
       </c>
       <c r="E93" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
@@ -4277,14 +4133,14 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-010.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C3IN-SD-011</t>
+          <t>R25-ARR1-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4293,13 +4149,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4050</v>
+        <v>2628.9</v>
       </c>
       <c r="D94" t="n">
-        <v>1287.8</v>
+        <v>101.6</v>
       </c>
       <c r="E94" t="n">
-        <v>6.35</v>
+        <v>40.2</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
@@ -4309,25 +4165,21 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>4050</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1287.8</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-011.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C3IN-SD-012</t>
+          <t>R25-ARR1-04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4336,13 +4188,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>857.88</v>
+        <v>2628.9</v>
       </c>
       <c r="D95" t="n">
-        <v>726.6</v>
+        <v>101.6</v>
       </c>
       <c r="E95" t="n">
-        <v>4.76</v>
+        <v>40.2</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -4352,25 +4204,21 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>857.88</v>
-      </c>
-      <c r="J95" t="n">
-        <v>726.6</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-012.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-04.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C3IN-SD-013</t>
+          <t>R25-ARR1-06</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4379,13 +4227,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>446.8</v>
+        <v>829.9</v>
       </c>
       <c r="D96" t="n">
-        <v>50.8</v>
+        <v>414.02</v>
       </c>
       <c r="E96" t="n">
-        <v>50.8</v>
+        <v>7.94</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -4402,14 +4250,14 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-013.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-06.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C3IN-SD-014</t>
+          <t>R25-ARR1-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4418,13 +4266,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3025.4</v>
+        <v>696.3</v>
       </c>
       <c r="D97" t="n">
-        <v>76.2</v>
+        <v>243.77</v>
       </c>
       <c r="E97" t="n">
-        <v>50.8</v>
+        <v>4.76</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
@@ -4441,14 +4289,14 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-014.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C3IN-SD-015</t>
+          <t>R25-ARR1-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4457,13 +4305,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>500</v>
+        <v>687.5</v>
       </c>
       <c r="D98" t="n">
-        <v>101.6</v>
+        <v>38.1</v>
       </c>
       <c r="E98" t="n">
-        <v>50.8</v>
+        <v>38.1</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
@@ -4480,14 +4328,14 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-015.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-08.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C3IN-SD-016</t>
+          <t>R25-ARR1-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4496,13 +4344,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1373.9</v>
+        <v>540</v>
       </c>
       <c r="D99" t="n">
-        <v>101.6</v>
+        <v>112.82</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>4.76</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
@@ -4519,14 +4367,14 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-016.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-09.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C3IN-SD-017</t>
+          <t>R25-ARR1-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4535,10 +4383,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>857.88</v>
+        <v>695.9</v>
       </c>
       <c r="D100" t="n">
-        <v>177.8</v>
+        <v>101.6</v>
       </c>
       <c r="E100" t="n">
         <v>4.76</v>
@@ -4551,25 +4399,21 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>857.88</v>
-      </c>
-      <c r="J100" t="n">
-        <v>177.8</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-017.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-10.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C3IN-SD-018</t>
+          <t>R25-ARR1-AD-01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4578,13 +4422,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2020.2</v>
+        <v>2628.9</v>
       </c>
       <c r="D101" t="n">
         <v>101.6</v>
       </c>
       <c r="E101" t="n">
-        <v>76.2</v>
+        <v>40.2</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
@@ -4601,14 +4445,14 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-018.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-AD-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C3IN-SD-018A</t>
+          <t>R25-ARR1-AD-02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4617,13 +4461,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2020.2</v>
+        <v>2628.9</v>
       </c>
       <c r="D102" t="n">
         <v>101.6</v>
       </c>
       <c r="E102" t="n">
-        <v>76.2</v>
+        <v>40.2</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
@@ -4640,14 +4484,14 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-018A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR1-AD-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C3IN-SD-019</t>
+          <t>R25-ARR2-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4656,13 +4500,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>446</v>
+        <v>2489.2</v>
       </c>
       <c r="D103" t="n">
         <v>76.2</v>
       </c>
       <c r="E103" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -4679,14 +4523,14 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-019.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C3IN-SD-020</t>
+          <t>R25-ARR2-03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4695,13 +4539,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>563.3200000000001</v>
+        <v>2413</v>
       </c>
       <c r="D104" t="n">
-        <v>435.3</v>
+        <v>96.53</v>
       </c>
       <c r="E104" t="n">
-        <v>9.52</v>
+        <v>3.18</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
@@ -4711,25 +4555,21 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>563.3200000000001</v>
-      </c>
-      <c r="J104" t="n">
-        <v>435.3</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-020.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C3IN-SD-021</t>
+          <t>R25-ARR2-04</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4738,13 +4578,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>520</v>
+        <v>2300</v>
       </c>
       <c r="D105" t="n">
-        <v>50.8</v>
+        <v>632.36</v>
       </c>
       <c r="E105" t="n">
-        <v>50.8</v>
+        <v>3.18</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
@@ -4761,14 +4601,14 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-021.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-04.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C3IN-SD-022</t>
+          <t>R25-ARR2-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4777,13 +4617,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>400</v>
+        <v>2021.7</v>
       </c>
       <c r="D106" t="n">
-        <v>300</v>
+        <v>101.6</v>
       </c>
       <c r="E106" t="n">
-        <v>4.76</v>
+        <v>25.4</v>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
@@ -4793,25 +4633,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>400</v>
-      </c>
-      <c r="J106" t="n">
-        <v>300</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-022.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-05.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C3IN-SD-023</t>
+          <t>R25-ARR2-06</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4820,13 +4656,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>898.4</v>
+        <v>680</v>
       </c>
       <c r="D107" t="n">
-        <v>50.8</v>
+        <v>76.2</v>
       </c>
       <c r="E107" t="n">
-        <v>50.8</v>
+        <v>4.76</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
@@ -4836,21 +4672,25 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>680</v>
+      </c>
+      <c r="J107" t="n">
+        <v>76.2</v>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-023.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-06.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C3IN-SD-024</t>
+          <t>R25-ARR2-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4859,13 +4699,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7480</v>
+        <v>594.1</v>
       </c>
       <c r="D108" t="n">
-        <v>63</v>
+        <v>76.2</v>
       </c>
       <c r="E108" t="n">
-        <v>48</v>
+        <v>6.35</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
@@ -4882,14 +4722,14 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-024.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C3IN-SD-025</t>
+          <t>R25-ARR2-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4898,13 +4738,13 @@
         </is>
       </c>
       <c r="C109" t="n">
+        <v>601.3</v>
+      </c>
+      <c r="D109" t="n">
         <v>101.6</v>
       </c>
-      <c r="D109" t="n">
-        <v>50.8</v>
-      </c>
       <c r="E109" t="n">
-        <v>6.35</v>
+        <v>9.52</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
@@ -4914,25 +4754,21 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="J109" t="n">
-        <v>50.8</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-025.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-08.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C3IN-SD-026</t>
+          <t>R25-ARR2-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4941,13 +4777,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>215.9</v>
+        <v>679.5</v>
       </c>
       <c r="D110" t="n">
         <v>76.2</v>
       </c>
       <c r="E110" t="n">
-        <v>6.35</v>
+        <v>9.52</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
@@ -4957,25 +4793,21 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>215.9</v>
-      </c>
-      <c r="J110" t="n">
-        <v>76.2</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-026.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-09.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C3IN-SD-027</t>
+          <t>R25-ARR2-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4984,13 +4816,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>328.06</v>
+        <v>579.2</v>
       </c>
       <c r="D111" t="n">
-        <v>92.08</v>
+        <v>76.2</v>
       </c>
       <c r="E111" t="n">
-        <v>3.18</v>
+        <v>9.52</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
@@ -5000,25 +4832,21 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I111" t="n">
-        <v>328.06</v>
-      </c>
-      <c r="J111" t="n">
-        <v>92.08</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-027.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-10.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C3IN-SD-028</t>
+          <t>R25-ARR2-AD-01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5027,13 +4855,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>339.16</v>
+        <v>2489.2</v>
       </c>
       <c r="D112" t="n">
-        <v>92.08</v>
+        <v>76.2</v>
       </c>
       <c r="E112" t="n">
-        <v>3.18</v>
+        <v>50.8</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
@@ -5043,25 +4871,21 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>339.82</v>
-      </c>
-      <c r="J112" t="n">
-        <v>92.08</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-028.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-AD-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C3IN-SD-029</t>
+          <t>R25-ARR2-AD-06</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5070,10 +4894,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>217.65</v>
+        <v>732.84</v>
       </c>
       <c r="D113" t="n">
-        <v>92.08</v>
+        <v>123.39</v>
       </c>
       <c r="E113" t="n">
         <v>3.18</v>
@@ -5090,21 +4914,21 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>217.65</v>
+        <v>732.84</v>
       </c>
       <c r="J113" t="n">
-        <v>92.08</v>
+        <v>123.39</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-029.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-AD-06.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C3IN-SD-030</t>
+          <t>R25-ARR2-AD-07</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5113,13 +4937,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>149.38</v>
+        <v>727.2</v>
       </c>
       <c r="D114" t="n">
-        <v>92.08</v>
+        <v>101.6</v>
       </c>
       <c r="E114" t="n">
-        <v>3.18</v>
+        <v>50.8</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
@@ -5129,25 +4953,21 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>149.59</v>
-      </c>
-      <c r="J114" t="n">
-        <v>92.08</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-030.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-AD-07.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C3IN-SD-031</t>
+          <t>R25-ARR2-AÑ-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5156,13 +4976,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>127</v>
+        <v>599</v>
       </c>
       <c r="D115" t="n">
-        <v>63.5</v>
+        <v>145</v>
       </c>
       <c r="E115" t="n">
-        <v>63.5</v>
+        <v>6.35</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
@@ -5172,21 +4992,25 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>599</v>
+      </c>
+      <c r="J115" t="n">
+        <v>145</v>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-031.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR2-AÑ-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C3IN-SD-033</t>
+          <t>R25-ARR3-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5195,13 +5019,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>616</v>
+        <v>2286</v>
       </c>
       <c r="D116" t="n">
-        <v>50.8</v>
+        <v>657.65</v>
       </c>
       <c r="E116" t="n">
-        <v>50.8</v>
+        <v>6.35</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
@@ -5211,21 +5035,25 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2286</v>
+      </c>
+      <c r="J116" t="n">
+        <v>657.65</v>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-033.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR3-01.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C3IN-SD-035</t>
+          <t>R25-ARR3-02</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5234,13 +5062,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>422</v>
+        <v>2286</v>
       </c>
       <c r="D117" t="n">
-        <v>50.8</v>
+        <v>137.82</v>
       </c>
       <c r="E117" t="n">
-        <v>50.8</v>
+        <v>6.35</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
@@ -5250,21 +5078,25 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>2286</v>
+      </c>
+      <c r="J117" t="n">
+        <v>137.82</v>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-035.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR3-02.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C3IN-SD-036</t>
+          <t>R25-ARR3-03</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5273,13 +5105,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>638</v>
+        <v>547</v>
       </c>
       <c r="D118" t="n">
-        <v>50.8</v>
+        <v>41.3</v>
       </c>
       <c r="E118" t="n">
-        <v>50.8</v>
+        <v>6.35</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
@@ -5289,21 +5121,25 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>547</v>
+      </c>
+      <c r="J118" t="n">
+        <v>41.3</v>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-036.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-ARR3-03.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C3IN-SD-037</t>
+          <t>R25-BAS1-001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5312,13 +5148,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2710</v>
+        <v>3266.19</v>
       </c>
       <c r="D119" t="n">
-        <v>15.88</v>
+        <v>170</v>
       </c>
       <c r="E119" t="n">
-        <v>15.88</v>
+        <v>6.35</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
@@ -5335,14 +5171,14 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-037.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C3IN-SD-038</t>
+          <t>R25-BAS1-002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5351,13 +5187,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3370</v>
+        <v>265</v>
       </c>
       <c r="D120" t="n">
-        <v>38.1</v>
+        <v>50.8</v>
       </c>
       <c r="E120" t="n">
-        <v>38.1</v>
+        <v>50.8</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
@@ -5374,14 +5210,14 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-038.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-002.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C3IN-SD-039</t>
+          <t>R25-BAS1-003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5390,13 +5226,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1000</v>
+        <v>2203.45</v>
       </c>
       <c r="D121" t="n">
-        <v>38.1</v>
+        <v>50.8</v>
       </c>
       <c r="E121" t="n">
-        <v>38.1</v>
+        <v>50.8</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
@@ -5413,14 +5249,14 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-039.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-003.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C3IN-SD-040</t>
+          <t>R25-BAS1-004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5429,13 +5265,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="D122" t="n">
-        <v>38.1</v>
+        <v>160</v>
       </c>
       <c r="E122" t="n">
-        <v>38.1</v>
+        <v>6.35</v>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
@@ -5452,14 +5288,14 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-040.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-004.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C3IN-SD-041</t>
+          <t>R25-BAS1-005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5468,13 +5304,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1100</v>
+        <v>2203.45</v>
       </c>
       <c r="D123" t="n">
-        <v>38.1</v>
+        <v>371.05</v>
       </c>
       <c r="E123" t="n">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
@@ -5491,14 +5327,14 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-041.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-005.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C3IN-SD-042</t>
+          <t>R25-BAS1-007</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5507,13 +5343,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2650</v>
+        <v>2203.45</v>
       </c>
       <c r="D124" t="n">
-        <v>25.4</v>
+        <v>76.2</v>
       </c>
       <c r="E124" t="n">
-        <v>25.4</v>
+        <v>50.8</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
@@ -5530,14 +5366,14 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-042.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-007.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C3IN-SD-043</t>
+          <t>R25-BAS1-008</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5546,10 +5382,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>445</v>
+        <v>3019.2</v>
       </c>
       <c r="D125" t="n">
-        <v>50.8</v>
+        <v>76.2</v>
       </c>
       <c r="E125" t="n">
         <v>50.8</v>
@@ -5569,14 +5405,14 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-043.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS1-008.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C3IN-SD-044</t>
+          <t>R25-BAS2-001</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5585,13 +5421,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>70</v>
+        <v>3500</v>
       </c>
       <c r="D126" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="E126" t="n">
-        <v>6.35</v>
+        <v>50.8</v>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
@@ -5601,25 +5437,21 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I126" t="n">
-        <v>70</v>
-      </c>
-      <c r="J126" t="n">
-        <v>70</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-044.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-001.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C3IN-SD-045</t>
+          <t>R25-BAS2-002</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5628,13 +5460,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>950</v>
+        <v>199</v>
       </c>
       <c r="D127" t="n">
-        <v>106.4</v>
+        <v>76.2</v>
       </c>
       <c r="E127" t="n">
-        <v>43.21</v>
+        <v>50.8</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
@@ -5651,14 +5483,14 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-045.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-002.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C3IN-SD-046</t>
+          <t>R25-BAS2-003</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5667,13 +5499,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>43</v>
+        <v>910</v>
       </c>
       <c r="D128" t="n">
-        <v>43</v>
+        <v>76.2</v>
       </c>
       <c r="E128" t="n">
-        <v>3.18</v>
+        <v>50.8</v>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
@@ -5683,25 +5515,21 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I128" t="n">
-        <v>43</v>
-      </c>
-      <c r="J128" t="n">
-        <v>43</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-046.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-003.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C3IN-SD-047</t>
+          <t>R25-BAS2-004</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5710,13 +5538,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>638</v>
+        <v>4182.86</v>
       </c>
       <c r="D129" t="n">
-        <v>101.6</v>
+        <v>177.8</v>
       </c>
       <c r="E129" t="n">
-        <v>76.2</v>
+        <v>9.52</v>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
@@ -5733,14 +5561,14 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Costado\C3IN-SD-047.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-004.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C3IN-PL-1</t>
+          <t>R25-BAS2-005</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5749,13 +5577,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>928.01</v>
+        <v>1464</v>
       </c>
       <c r="D130" t="n">
-        <v>732.42</v>
+        <v>50.8</v>
       </c>
       <c r="E130" t="n">
-        <v>4.76</v>
+        <v>50.8</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -5772,14 +5600,14 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-1.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-005.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C3IN-PL-1A</t>
+          <t>R25-BAS2-006</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5788,13 +5616,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>933.5</v>
+        <v>200</v>
       </c>
       <c r="D131" t="n">
-        <v>737.9</v>
+        <v>50.8</v>
       </c>
       <c r="E131" t="n">
-        <v>4.76</v>
+        <v>50.8</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
@@ -5804,25 +5632,21 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I131" t="n">
-        <v>933.45</v>
-      </c>
-      <c r="J131" t="n">
-        <v>737.86</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-1A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-006.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C3IN-PL-2</t>
+          <t>R25-BAS2-007</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5831,13 +5655,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1837.52</v>
+        <v>1954</v>
       </c>
       <c r="D132" t="n">
-        <v>203.2</v>
+        <v>50.8</v>
       </c>
       <c r="E132" t="n">
-        <v>1.9</v>
+        <v>50.8</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
@@ -5854,14 +5678,14 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-2.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-007.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C3IN-PL-3</t>
+          <t>R25-BAS2-009</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5870,10 +5694,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1020</v>
+        <v>1954</v>
       </c>
       <c r="D133" t="n">
-        <v>147.18</v>
+        <v>264</v>
       </c>
       <c r="E133" t="n">
         <v>3.18</v>
@@ -5893,14 +5717,14 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-3.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-009.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C3IN-PL-4</t>
+          <t>R25-BAS2-010</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5909,13 +5733,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1256.75</v>
+        <v>2203.45</v>
       </c>
       <c r="D134" t="n">
         <v>76.2</v>
       </c>
       <c r="E134" t="n">
-        <v>3.18</v>
+        <v>50.8</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
@@ -5932,14 +5756,14 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-4.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-010.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C3IN-PL-5</t>
+          <t>R25-BAS2-011</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5948,13 +5772,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1020</v>
+        <v>2061</v>
       </c>
       <c r="D135" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="E135" t="n">
         <v>50.8</v>
-      </c>
-      <c r="E135" t="n">
-        <v>4.76</v>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
@@ -5971,14 +5795,14 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-5.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-011.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C3IN-PL-6</t>
+          <t>R25-BAS2-012</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5987,13 +5811,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>636</v>
+        <v>200</v>
       </c>
       <c r="D136" t="n">
-        <v>38.1</v>
+        <v>112.9</v>
       </c>
       <c r="E136" t="n">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
@@ -6010,14 +5834,14 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Portallantas\C3IN-PL-6.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-012.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C3IN-PRA-001</t>
+          <t>R25-BAS2-013</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6026,13 +5850,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1822</v>
+        <v>1424</v>
       </c>
       <c r="D137" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="E137" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
@@ -6049,14 +5873,14 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Puente RAR\C3IN-PRA-001.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-013.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C3IN-PRA-002</t>
+          <t>R25-BAS2-014</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6065,13 +5889,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>400</v>
+        <v>1034.2</v>
       </c>
       <c r="D138" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="E138" t="n">
-        <v>76.2</v>
+        <v>50.8</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
@@ -6088,14 +5912,14 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Puente RAR\C3IN-PRA-002.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-014.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C3IN-PRA-003</t>
+          <t>R25-BAS2-016</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6104,13 +5928,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>655.2</v>
+        <v>1538.72</v>
       </c>
       <c r="D139" t="n">
-        <v>518.4</v>
+        <v>559.64</v>
       </c>
       <c r="E139" t="n">
-        <v>6.35</v>
+        <v>9.52</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
@@ -6120,21 +5944,25 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1211.2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1014.09</v>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Puente RAR\C3IN-PRA-003.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-016.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C3IN-PRA-003A</t>
+          <t>R25-BAS2-017</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6143,13 +5971,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>655.2</v>
+        <v>290.33</v>
       </c>
       <c r="D140" t="n">
-        <v>518.4</v>
+        <v>38.1</v>
       </c>
       <c r="E140" t="n">
-        <v>6.35</v>
+        <v>4.76</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
@@ -6163,14 +5991,3803 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>655.2</v>
+        <v>290.33</v>
       </c>
       <c r="J140" t="n">
-        <v>518.4299999999999</v>
+        <v>38.1</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>C:\Users\INGENIERIA-02\Desktop\Alejandro de Jesus Gonzalez Hdez\0-0 pruebas de dxf\C3 INTERNATIONAL 2026\PIEZAS\Puente RAR\C3IN-PRA-003A.SLDPRT</t>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-017.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>R25-BAS2-018</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>196.14</v>
+      </c>
+      <c r="D141" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>196.14</v>
+      </c>
+      <c r="J141" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS2-018.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>R25-BAS6-002</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="D142" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="E142" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS6-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>R25-BAS6-007</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>184.16</v>
+      </c>
+      <c r="D143" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BAS6-007.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>R25-BASFLO-001</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3188.8</v>
+      </c>
+      <c r="D144" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E144" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BASFLO-001.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>R25-BASFLO-002</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>470</v>
+      </c>
+      <c r="D145" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BASFLO-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>R25-BMFL-001</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>609.6</v>
+      </c>
+      <c r="D146" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-001.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>R25-BMFL-002</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2214.6</v>
+      </c>
+      <c r="D147" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E147" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>R25-BMFL-003</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>996</v>
+      </c>
+      <c r="D148" t="n">
+        <v>673.1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-003.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>R25-BMFL-004</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>635</v>
+      </c>
+      <c r="D149" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-004.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>R25-BMFL-005</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>609.6</v>
+      </c>
+      <c r="D150" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E150" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-005.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>R25-BMFL-006</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>625</v>
+      </c>
+      <c r="D151" t="n">
+        <v>170</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-006.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>R25-BMFL-007</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>736.6</v>
+      </c>
+      <c r="D152" t="n">
+        <v>449.73</v>
+      </c>
+      <c r="E152" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-007.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>R25-BMFL-008</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>632.6</v>
+      </c>
+      <c r="D153" t="n">
+        <v>238.99</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>632.6</v>
+      </c>
+      <c r="J153" t="n">
+        <v>238.99</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-008.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>R25-BMFL-009</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>609.6</v>
+      </c>
+      <c r="D154" t="n">
+        <v>115</v>
+      </c>
+      <c r="E154" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-009.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>R25-BMFL-010</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>690.6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-010.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>R25-BMFL-011</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>168.03</v>
+      </c>
+      <c r="D156" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E156" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-011.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>R25-BMFL-020</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>532.09</v>
+      </c>
+      <c r="J157" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-020.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>R25-BMFL-021</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>500</v>
+      </c>
+      <c r="D158" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E158" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-021.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>R25-BMFL-022</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="D159" t="n">
+        <v>449.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-022.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>R25-BMFL-023</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFL-023.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>R25-BMFLAÑ-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="D161" t="n">
+        <v>141.96</v>
+      </c>
+      <c r="E161" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-BMFLAÑ-01.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>R25-CAM-001</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D162" t="n">
+        <v>166.15</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J162" t="n">
+        <v>166.15</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-CAM-001.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>R25-CG-001</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2392.56</v>
+      </c>
+      <c r="D163" t="n">
+        <v>953</v>
+      </c>
+      <c r="E163" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-CG-001.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>R25-CG-002</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>203</v>
+      </c>
+      <c r="D164" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>203</v>
+      </c>
+      <c r="J164" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-CG-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>R25-CG-003</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>195</v>
+      </c>
+      <c r="D165" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E165" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>195</v>
+      </c>
+      <c r="J165" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-CG-003.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>R25-CG-004</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>203</v>
+      </c>
+      <c r="D166" t="n">
+        <v>182</v>
+      </c>
+      <c r="E166" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>203</v>
+      </c>
+      <c r="J166" t="n">
+        <v>182</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-CG-004.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>R25-COS-002</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2673</v>
+      </c>
+      <c r="D167" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E167" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>R25-COS-003</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>426</v>
+      </c>
+      <c r="D168" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E168" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-003.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>R25-COS-006</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="D169" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="E169" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="J169" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-006.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>R25-COS-007</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1552.4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>424.21</v>
+      </c>
+      <c r="E170" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-007.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>R25-COS-008</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>3267</v>
+      </c>
+      <c r="D171" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E171" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-008.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>R25-COS-009</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3267</v>
+      </c>
+      <c r="D172" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E172" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-009.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>R25-COS-010</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1512</v>
+      </c>
+      <c r="D173" t="n">
+        <v>354</v>
+      </c>
+      <c r="E173" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-010.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>R25-COS-011</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>4572.17</v>
+      </c>
+      <c r="D174" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="E174" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-011.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>R25-COS-012</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>4746.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="E175" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-012.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>R25-COS-013</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>4575.5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="E176" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-013.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>R25-COS-014</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>4746.5</v>
+      </c>
+      <c r="D177" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="E177" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-014.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>R25-COS-015</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>850</v>
+      </c>
+      <c r="D178" t="n">
+        <v>110</v>
+      </c>
+      <c r="E178" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-COS-015.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>R25-LGR-01</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>5970</v>
+      </c>
+      <c r="D179" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>5970</v>
+      </c>
+      <c r="J179" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-LGR-01.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>R25-LGR-02</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>5970</v>
+      </c>
+      <c r="D180" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="E180" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>5970</v>
+      </c>
+      <c r="J180" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-LGR-02.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>R25-PISO-BAS1</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D181" t="n">
+        <v>862.88</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-PISO-BAS1.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>R25-PISO-BAS2A</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>967</v>
+      </c>
+      <c r="D182" t="n">
+        <v>835</v>
+      </c>
+      <c r="E182" t="n">
+        <v>3</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-PISO-BAS2A.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>R25-PISO-BAS2B</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D183" t="n">
+        <v>835</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-PISO-BAS2B.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>R25-PISO-BAS2C</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1408</v>
+      </c>
+      <c r="D184" t="n">
+        <v>835</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1408</v>
+      </c>
+      <c r="J184" t="n">
+        <v>835</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-PISO-BAS2C.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS-6</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1276.03</v>
+      </c>
+      <c r="D185" t="n">
+        <v>669.45</v>
+      </c>
+      <c r="E185" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS-6.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS1</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D186" t="n">
+        <v>908.64</v>
+      </c>
+      <c r="E186" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS1.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS1A</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D187" t="n">
+        <v>215</v>
+      </c>
+      <c r="E187" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS1A.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS2A</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1504.6</v>
+      </c>
+      <c r="D188" t="n">
+        <v>649.65</v>
+      </c>
+      <c r="E188" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS2A.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS2B</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1304.6</v>
+      </c>
+      <c r="D189" t="n">
+        <v>790.05</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS2B.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS2C</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>973.2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>790.05</v>
+      </c>
+      <c r="E190" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS2C.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>R25-RAMP-BAS3</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1517.7</v>
+      </c>
+      <c r="D191" t="n">
+        <v>669.45</v>
+      </c>
+      <c r="E191" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-BAS3.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>R25-RAMP-RAR1</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1584</v>
+      </c>
+      <c r="D192" t="n">
+        <v>816.55</v>
+      </c>
+      <c r="E192" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-RAMP-RAR1.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>R25-TABCO</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>840</v>
+      </c>
+      <c r="D193" t="n">
+        <v>295</v>
+      </c>
+      <c r="E193" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>840</v>
+      </c>
+      <c r="J193" t="n">
+        <v>295</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TABCO.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>R25-TDM-001</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2590.8</v>
+      </c>
+      <c r="D194" t="n">
+        <v>483.83</v>
+      </c>
+      <c r="E194" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>2590.8</v>
+      </c>
+      <c r="J194" t="n">
+        <v>483.83</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-001.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>R25-TDM-002</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2679.7</v>
+      </c>
+      <c r="D195" t="n">
+        <v>463.25</v>
+      </c>
+      <c r="E195" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-002.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>R25-TDM-003</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2438.4</v>
+      </c>
+      <c r="D196" t="n">
+        <v>558.99</v>
+      </c>
+      <c r="E196" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-003.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>R25-TDM-004</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>749.35</v>
+      </c>
+      <c r="D197" t="n">
+        <v>681.1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-004.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>R25-TDM-005</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>876</v>
+      </c>
+      <c r="D198" t="n">
+        <v>610</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-005.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>R25-TDM-006</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>854</v>
+      </c>
+      <c r="D199" t="n">
+        <v>610</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-006.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>R25-TDM-007</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="D200" t="n">
+        <v>584</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1170.76</v>
+      </c>
+      <c r="J200" t="n">
+        <v>584</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-007.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>R25-TDM-008</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D201" t="n">
+        <v>194</v>
+      </c>
+      <c r="E201" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-008.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>R25-TDM-009</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>975</v>
+      </c>
+      <c r="D202" t="n">
+        <v>222.36</v>
+      </c>
+      <c r="E202" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-009.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>R25-TDM-010</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2266</v>
+      </c>
+      <c r="D203" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-010.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>R25-TDM-011</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>677</v>
+      </c>
+      <c r="D204" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-011.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>R25-TDM-012</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>616</v>
+      </c>
+      <c r="D205" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-012.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>R25-TDM-013</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="D206" t="n">
+        <v>610.1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-013.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>R25-TDM-014</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>616</v>
+      </c>
+      <c r="D207" t="n">
+        <v>349</v>
+      </c>
+      <c r="E207" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>616</v>
+      </c>
+      <c r="J207" t="n">
+        <v>349</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-014.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>R25-TDM-016</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D208" t="n">
+        <v>232.56</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>2428</v>
+      </c>
+      <c r="J208" t="n">
+        <v>232.56</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-016.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>R25-TDM-017</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>500</v>
+      </c>
+      <c r="D209" t="n">
+        <v>260</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-017.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>R25-TDM-018</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>442</v>
+      </c>
+      <c r="D210" t="n">
+        <v>42</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>442</v>
+      </c>
+      <c r="J210" t="n">
+        <v>42</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-018.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>R25-TDM-019</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>477</v>
+      </c>
+      <c r="D211" t="n">
+        <v>42</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>477</v>
+      </c>
+      <c r="J211" t="n">
+        <v>42</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-019.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>R25-TDM-020</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D212" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1055</v>
+      </c>
+      <c r="J212" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-020.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>R25-TDM-021</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>563</v>
+      </c>
+      <c r="D213" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\R25-TDM-021.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>RB-04A</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>508</v>
+      </c>
+      <c r="D214" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="E214" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\RB-04A.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>RC3-LG-EST</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>954.17</v>
+      </c>
+      <c r="D215" t="n">
+        <v>188</v>
+      </c>
+      <c r="E215" t="n">
+        <v>3</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\RC3-LG-EST.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SCA-CB1-002-P</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="E216" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CB1-002-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SCA-CB1-003-P</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D217" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CB1-003-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SCA-CF1-014-P</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>90</v>
+      </c>
+      <c r="D218" t="n">
+        <v>90</v>
+      </c>
+      <c r="E218" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>90</v>
+      </c>
+      <c r="J218" t="n">
+        <v>90</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CF1-014-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SCA-CF2-009-M</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="D219" t="n">
+        <v>24</v>
+      </c>
+      <c r="E219" t="n">
+        <v>24</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CF2-009-M.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SCA-CF2-017-L</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>190</v>
+      </c>
+      <c r="D220" t="n">
+        <v>100</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CF2-017-L.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SCA-CQT1-01-L</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>350</v>
+      </c>
+      <c r="D221" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="E221" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CQT1-01-L.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SCA-CQT2-01-L</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>350</v>
+      </c>
+      <c r="D222" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="E222" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-CQT2-01-L.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SCA-GB1-002-P</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="D223" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E223" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-GB1-002-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SCA-GB1-003-P</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D224" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="E224" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-GB1-003-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SCA-IV-001-L</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>254</v>
+      </c>
+      <c r="D225" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-001-L.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SCA-IV-002-SS-M</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D226" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E226" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-002-SS-M.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SCA-IV-003-L-D</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>254</v>
+      </c>
+      <c r="D227" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>254</v>
+      </c>
+      <c r="J227" t="n">
+        <v>101.58</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-003-L-D.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SCA-IV-004-SS</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>550</v>
+      </c>
+      <c r="D228" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E228" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-004-SS.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SCA-IV-005-L-D</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>150</v>
+      </c>
+      <c r="D229" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-005-L-D.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SCA-IV-006</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E230" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-IV-006.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SCA-PRR-001-P</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>154</v>
+      </c>
+      <c r="E231" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-PRR-001-P.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SCA-PRR-005-P-M</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D232" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="E232" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-PRR-005-P-M.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SCA-TBX-001-L-D</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1219.2</v>
+      </c>
+      <c r="D233" t="n">
+        <v>675.13</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-TBX-001-L-D.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SCA-TBX-002-L-D</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D234" t="n">
+        <v>402</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-TBX-002-L-D.SLDPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SCA-TBX-003-L-D</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>.sldprt</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>417.05</v>
+      </c>
+      <c r="D235" t="n">
+        <v>407.05</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>C:\Users\INGENIERIA-02\Desktop\CAD_PENDIENTES\SCA-TBX-003-L-D.SLDPRT</t>
         </is>
       </c>
     </row>
